--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -34,6 +34,7 @@
     <definedName function="false" hidden="false" name="Budget_Q4_2023" vbProcedure="false">Summary!$B$2</definedName>
     <definedName function="false" hidden="false" name="Budget_Q4_2024" vbProcedure="false">Summary!$B$6</definedName>
     <definedName function="false" hidden="false" name="Budget_Q4_2025" vbProcedure="false">Summary!$B$10</definedName>
+    <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
     <definedName function="false" hidden="false" name="Variance_Q1_2024" vbProcedure="false">Summary!$D$3</definedName>
     <definedName function="false" hidden="false" name="Variance_Q1_2025" vbProcedure="false">Summary!$D$7</definedName>
     <definedName function="false" hidden="false" name="Variance_Q1_2026" vbProcedure="false">Summary!$D$11</definedName>
@@ -115,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T08:51:04+00:00</t>
+    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -207,16 +208,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -240,252 +237,252 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <v>18500000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="0" t="n">
         <v>18500000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="0" t="n">
         <f aca="false">C2-B2</f>
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">ROUND(D2/B2,4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>26000000</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <v>27253000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="0" t="n">
         <f aca="false">C3-B3</f>
         <v>1253000</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">ROUND(D3/B3,4)</f>
         <v>0.0482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="0" t="n">
         <v>26000000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="0" t="n">
         <v>26670000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="0" t="n">
         <f aca="false">C4-B4</f>
         <v>670000</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">ROUND(D4/B4,4)</f>
         <v>0.0258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <v>26000000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="0" t="n">
         <v>25106000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <f aca="false">C5-B5</f>
         <v>-894000</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">ROUND(D5/B5,4)</f>
         <v>-0.0344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <v>26000000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <v>24852000</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <f aca="false">C6-B6</f>
         <v>-1148000</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">ROUND(D6/B6,4)</f>
         <v>-0.0442</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <v>34500000</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="0" t="n">
         <v>34871000</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <f aca="false">C7-B7</f>
         <v>371000</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">ROUND(D7/B7,4)</f>
         <v>0.0108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <v>34500000</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <v>36222000</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">C8-B8</f>
         <v>1722000</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">ROUND(D8/B8,4)</f>
         <v>0.0499</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <v>34500000</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="0" t="n">
         <v>35050000</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="0" t="n">
         <f aca="false">C9-B9</f>
         <v>550000</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">ROUND(D9/B9,4)</f>
         <v>0.0159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="0" t="n">
         <v>34500000</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <v>33072000</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <f aca="false">C10-B10</f>
         <v>-1428000</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">ROUND(D10/B10,4)</f>
         <v>-0.0414</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="0" t="n">
         <v>42000000</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="0" t="n">
         <v>40400000</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="0" t="n">
         <f aca="false">C11-B11</f>
         <v>-1600000</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">ROUND(D11/B11,4)</f>
         <v>-0.0381</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="0" t="n">
         <v>42000000</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="0" t="n">
         <v>42882000</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <f aca="false">C12-B12</f>
         <v>882000</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">ROUND(D12/B12,4)</f>
         <v>0.021</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="0" t="n">
         <f aca="false">SUM(B2:B12)</f>
         <v>344500000</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="0" t="n">
         <f aca="false">SUM(C2:C12)</f>
         <v>344878000</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="0" t="n">
         <f aca="false">C13-B13</f>
         <v>378000</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="0" t="n">
         <f aca="false">ROUND(D13/B13,4)</f>
         <v>0.0011</v>
       </c>
@@ -510,31 +507,31 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>22</v>
       </c>
     </row>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
+    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
+    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">demo_today</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15</t>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
 </sst>
 </file>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
+    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
+    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
+    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
+    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
+    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
+    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Budget_vs_Actual_2026.xlsx
+++ b/seed_data/excel/Budget_vs_Actual_2026.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
+    <t xml:space="preserve">2026-10-12T13:12:20+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
